--- a/modeleLogiqueCorps/ig/StructureDefinition-fr-cda-raison-de-la-recommandation.xlsx
+++ b/modeleLogiqueCorps/ig/StructureDefinition-fr-cda-raison-de-la-recommandation.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3399" uniqueCount="343">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3413" uniqueCount="357">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T12:22:25+00:00</t>
+    <t>2026-06-30T08:22:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -508,6 +508,9 @@
 </t>
   </si>
   <si>
+    <t>Can serve as a target of a linkHtml reference</t>
+  </si>
+  <si>
     <t>Section.classCode</t>
   </si>
   <si>
@@ -697,6 +700,9 @@
     <t>Titre de la section</t>
   </si>
   <si>
+    <t>If valued, it is to be rendered as part of the narrative content of the clinical document body.</t>
+  </si>
+  <si>
     <t>Section.text</t>
   </si>
   <si>
@@ -707,10 +713,25 @@
     <t>Bloc narratif</t>
   </si>
   <si>
+    <t>Also referred to as the CDA Narrative Block</t>
+  </si>
+  <si>
     <t>Section.confidentialityCode</t>
   </si>
   <si>
+    <t>Controls the disclosure of information in this section</t>
+  </si>
+  <si>
+    <t>A value for Section.confidentialityCode overrides the value propagated from StructuredBody.</t>
+  </si>
+  <si>
     <t>Section.languageCode</t>
+  </si>
+  <si>
+    <t>Human language of character data</t>
+  </si>
+  <si>
+    <t>A value for Section.languageCode overrides the value propagated from StructuredBody.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/all-languages</t>
@@ -723,6 +744,15 @@
 </t>
   </si>
   <si>
+    <t>Primary target of the entries recorded in a section</t>
+  </si>
+  <si>
+    <t>Most of the time the subject is the same as the recordTarget, but need not be, for instance when the subject is a fetus observed in an obstetrical ultrasound.</t>
+  </si>
+  <si>
+    <t>The subject participant can be ascribed to a CDA section or a CDA entry. It propagates to nested components, unless overridden. The subject of a document is presumed to be the patient.</t>
+  </si>
+  <si>
     <t>Section.author</t>
   </si>
   <si>
@@ -730,6 +760,9 @@
 </t>
   </si>
   <si>
+    <t>The author participant can be ascribed to a CDA section, where it overrides the value(s) propagated from the CDA header.</t>
+  </si>
+  <si>
     <t>Section.informant</t>
   </si>
   <si>
@@ -737,6 +770,9 @@
 </t>
   </si>
   <si>
+    <t>The informant participant can be ascribed to a CDA section where it overrides the value(s) propagated from the CDA header.</t>
+  </si>
+  <si>
     <t>Section.entry</t>
   </si>
   <si>
@@ -1036,6 +1072,12 @@
   <si>
     <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/InfrastructureRoot
 </t>
+  </si>
+  <si>
+    <t>Used to nest a Section within a Section</t>
+  </si>
+  <si>
+    <t>Context propagates to nested sections</t>
   </si>
   <si>
     <t>Section.component.nullFlavor</t>
@@ -1412,7 +1454,7 @@
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="13.4296875" customWidth="true" bestFit="true"/>
+    <col min="15" max="15" width="148.87109375" customWidth="true" bestFit="true"/>
     <col min="16" max="16" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
@@ -4451,7 +4493,9 @@
       <c r="K30" t="s" s="2">
         <v>159</v>
       </c>
-      <c r="L30" s="2"/>
+      <c r="L30" t="s" s="2">
+        <v>160</v>
+      </c>
       <c r="M30" s="2"/>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4522,10 +4566,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4559,7 +4603,7 @@
       </c>
       <c r="Q31" s="2"/>
       <c r="R31" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="S31" t="s" s="2">
         <v>74</v>
@@ -4581,7 +4625,7 @@
       </c>
       <c r="Y31" s="2"/>
       <c r="Z31" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>74</v>
@@ -4599,7 +4643,7 @@
         <v>74</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -4619,10 +4663,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4656,7 +4700,7 @@
       </c>
       <c r="Q32" s="2"/>
       <c r="R32" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="S32" t="s" s="2">
         <v>74</v>
@@ -4678,7 +4722,7 @@
       </c>
       <c r="Y32" s="2"/>
       <c r="Z32" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>74</v>
@@ -4696,7 +4740,7 @@
         <v>74</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -4716,10 +4760,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4733,7 +4777,7 @@
         <v>75</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>74</v>
@@ -4745,10 +4789,10 @@
         <v>95</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -4799,7 +4843,7 @@
         <v>74</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -4819,10 +4863,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4836,7 +4880,7 @@
         <v>75</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>74</v>
@@ -4845,13 +4889,13 @@
         <v>74</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -4902,7 +4946,7 @@
         <v>74</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -4922,10 +4966,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5023,10 +5067,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5042,7 +5086,7 @@
         <v>75</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>74</v>
@@ -5055,7 +5099,7 @@
       </c>
       <c r="L36" s="2"/>
       <c r="M36" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5067,7 +5111,7 @@
         <v>74</v>
       </c>
       <c r="S36" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="T36" t="s" s="2">
         <v>74</v>
@@ -5106,7 +5150,7 @@
         <v>74</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -5126,17 +5170,17 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E37" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F37" t="s" s="2">
         <v>75</v>
@@ -5145,7 +5189,7 @@
         <v>75</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>74</v>
@@ -5158,7 +5202,7 @@
       </c>
       <c r="L37" s="2"/>
       <c r="M37" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5170,7 +5214,7 @@
         <v>74</v>
       </c>
       <c r="S37" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="T37" t="s" s="2">
         <v>74</v>
@@ -5209,7 +5253,7 @@
         <v>74</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -5229,17 +5273,17 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E38" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F38" t="s" s="2">
         <v>80</v>
@@ -5261,7 +5305,7 @@
       </c>
       <c r="L38" s="2"/>
       <c r="M38" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5273,7 +5317,7 @@
         <v>74</v>
       </c>
       <c r="S38" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="T38" t="s" s="2">
         <v>74</v>
@@ -5312,7 +5356,7 @@
         <v>74</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -5332,17 +5376,17 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E39" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F39" t="s" s="2">
         <v>80</v>
@@ -5364,7 +5408,7 @@
       </c>
       <c r="L39" s="2"/>
       <c r="M39" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5415,7 +5459,7 @@
         <v>74</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -5435,17 +5479,17 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E40" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F40" t="s" s="2">
         <v>75</v>
@@ -5454,7 +5498,7 @@
         <v>75</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>74</v>
@@ -5467,7 +5511,7 @@
       </c>
       <c r="L40" s="2"/>
       <c r="M40" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -5479,7 +5523,7 @@
         <v>74</v>
       </c>
       <c r="S40" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="T40" t="s" s="2">
         <v>74</v>
@@ -5518,7 +5562,7 @@
         <v>74</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -5538,10 +5582,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5564,11 +5608,11 @@
         <v>74</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="L41" s="2"/>
       <c r="M41" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -5619,7 +5663,7 @@
         <v>74</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -5639,10 +5683,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -5669,7 +5713,7 @@
       </c>
       <c r="L42" s="2"/>
       <c r="M42" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -5720,7 +5764,7 @@
         <v>74</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -5740,17 +5784,17 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E43" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F43" t="s" s="2">
         <v>80</v>
@@ -5768,11 +5812,11 @@
         <v>74</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="L43" s="2"/>
       <c r="M43" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -5823,7 +5867,7 @@
         <v>74</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -5843,17 +5887,17 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E44" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F44" t="s" s="2">
         <v>80</v>
@@ -5871,11 +5915,11 @@
         <v>74</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L44" s="2"/>
       <c r="M44" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -5926,7 +5970,7 @@
         <v>74</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -5946,17 +5990,17 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E45" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F45" t="s" s="2">
         <v>80</v>
@@ -5974,11 +6018,11 @@
         <v>74</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L45" s="2"/>
       <c r="M45" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6029,7 +6073,7 @@
         <v>74</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -6049,10 +6093,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6066,7 +6110,7 @@
         <v>75</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>74</v>
@@ -6075,16 +6119,18 @@
         <v>74</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="N46" s="2"/>
-      <c r="O46" s="2"/>
+      <c r="O46" t="s" s="2">
+        <v>222</v>
+      </c>
       <c r="P46" t="s" s="2">
         <v>74</v>
       </c>
@@ -6132,7 +6178,7 @@
         <v>74</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -6152,10 +6198,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6169,7 +6215,7 @@
         <v>75</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>74</v>
@@ -6178,15 +6224,17 @@
         <v>74</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="N47" s="2"/>
+        <v>225</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>226</v>
+      </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>74</v>
@@ -6235,7 +6283,7 @@
         <v>74</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -6255,10 +6303,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6281,12 +6329,16 @@
         <v>74</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="L48" s="2"/>
+        <v>171</v>
+      </c>
+      <c r="L48" t="s" s="2">
+        <v>228</v>
+      </c>
       <c r="M48" s="2"/>
       <c r="N48" s="2"/>
-      <c r="O48" s="2"/>
+      <c r="O48" t="s" s="2">
+        <v>229</v>
+      </c>
       <c r="P48" t="s" s="2">
         <v>74</v>
       </c>
@@ -6334,7 +6386,7 @@
         <v>74</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -6354,10 +6406,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6382,10 +6434,14 @@
       <c r="K49" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="L49" s="2"/>
+      <c r="L49" t="s" s="2">
+        <v>231</v>
+      </c>
       <c r="M49" s="2"/>
       <c r="N49" s="2"/>
-      <c r="O49" s="2"/>
+      <c r="O49" t="s" s="2">
+        <v>232</v>
+      </c>
       <c r="P49" t="s" s="2">
         <v>74</v>
       </c>
@@ -6413,7 +6469,7 @@
       </c>
       <c r="Y49" s="2"/>
       <c r="Z49" t="s" s="2">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>74</v>
@@ -6431,7 +6487,7 @@
         <v>74</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -6451,10 +6507,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -6477,12 +6533,18 @@
         <v>74</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="L50" s="2"/>
+        <v>235</v>
+      </c>
+      <c r="L50" t="s" s="2">
+        <v>236</v>
+      </c>
       <c r="M50" s="2"/>
-      <c r="N50" s="2"/>
-      <c r="O50" s="2"/>
+      <c r="N50" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="O50" t="s" s="2">
+        <v>238</v>
+      </c>
       <c r="P50" t="s" s="2">
         <v>74</v>
       </c>
@@ -6530,7 +6592,7 @@
         <v>74</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -6550,10 +6612,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -6576,12 +6638,14 @@
         <v>74</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="L51" s="2"/>
       <c r="M51" s="2"/>
       <c r="N51" s="2"/>
-      <c r="O51" s="2"/>
+      <c r="O51" t="s" s="2">
+        <v>241</v>
+      </c>
       <c r="P51" t="s" s="2">
         <v>74</v>
       </c>
@@ -6629,7 +6693,7 @@
         <v>74</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -6649,10 +6713,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>231</v>
+        <v>242</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>231</v>
+        <v>242</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -6675,12 +6739,14 @@
         <v>74</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>232</v>
+        <v>243</v>
       </c>
       <c r="L52" s="2"/>
       <c r="M52" s="2"/>
       <c r="N52" s="2"/>
-      <c r="O52" s="2"/>
+      <c r="O52" t="s" s="2">
+        <v>244</v>
+      </c>
       <c r="P52" t="s" s="2">
         <v>74</v>
       </c>
@@ -6728,7 +6794,7 @@
         <v>74</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>231</v>
+        <v>242</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -6748,10 +6814,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -6759,13 +6825,13 @@
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="G53" t="s" s="2">
         <v>81</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>74</v>
@@ -6774,7 +6840,7 @@
         <v>74</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="L53" s="2"/>
       <c r="M53" s="2"/>
@@ -6815,7 +6881,7 @@
         <v>74</v>
       </c>
       <c r="AB53" t="s" s="2">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="AC53" s="2"/>
       <c r="AD53" t="s" s="2">
@@ -6825,7 +6891,7 @@
         <v>124</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -6845,13 +6911,13 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>237</v>
+        <v>249</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="C54" t="s" s="2">
-        <v>238</v>
+        <v>250</v>
       </c>
       <c r="D54" t="s" s="2">
         <v>74</v>
@@ -6873,7 +6939,7 @@
         <v>74</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="L54" s="2"/>
       <c r="M54" s="2"/>
@@ -6926,7 +6992,7 @@
         <v>74</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -6946,10 +7012,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>240</v>
+        <v>252</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7047,10 +7113,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7148,10 +7214,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7249,10 +7315,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -7350,10 +7416,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>247</v>
+        <v>259</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>248</v>
+        <v>260</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -7453,10 +7519,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -7556,10 +7622,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -7659,10 +7725,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>253</v>
+        <v>265</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>254</v>
+        <v>266</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -7762,10 +7828,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>255</v>
+        <v>267</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>256</v>
+        <v>268</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -7863,10 +7929,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>258</v>
+        <v>270</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -7896,7 +7962,7 @@
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="Q64" s="2"/>
       <c r="R64" t="s" s="2">
@@ -7922,7 +7988,7 @@
       </c>
       <c r="Y64" s="2"/>
       <c r="Z64" t="s" s="2">
-        <v>260</v>
+        <v>272</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>74</v>
@@ -7940,7 +8006,7 @@
         <v>74</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -7960,10 +8026,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>262</v>
+        <v>274</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -7997,7 +8063,7 @@
       </c>
       <c r="Q65" s="2"/>
       <c r="R65" t="s" s="2">
-        <v>264</v>
+        <v>276</v>
       </c>
       <c r="S65" t="s" s="2">
         <v>74</v>
@@ -8039,7 +8105,7 @@
         <v>74</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>265</v>
+        <v>277</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -8059,10 +8125,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>266</v>
+        <v>278</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>267</v>
+        <v>279</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8085,7 +8151,7 @@
         <v>74</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>268</v>
+        <v>280</v>
       </c>
       <c r="L66" s="2"/>
       <c r="M66" s="2"/>
@@ -8138,7 +8204,7 @@
         <v>74</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -8158,10 +8224,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>270</v>
+        <v>282</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -8184,7 +8250,7 @@
         <v>74</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="L67" s="2"/>
       <c r="M67" s="2"/>
@@ -8237,7 +8303,7 @@
         <v>74</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -8257,10 +8323,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>274</v>
+        <v>286</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>275</v>
+        <v>287</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -8283,10 +8349,10 @@
         <v>74</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>277</v>
+        <v>289</v>
       </c>
       <c r="M68" s="2"/>
       <c r="N68" s="2"/>
@@ -8338,7 +8404,7 @@
         <v>74</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>278</v>
+        <v>290</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -8358,10 +8424,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>280</v>
+        <v>292</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -8384,7 +8450,7 @@
         <v>74</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>281</v>
+        <v>293</v>
       </c>
       <c r="L69" s="2"/>
       <c r="M69" s="2"/>
@@ -8437,7 +8503,7 @@
         <v>74</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>282</v>
+        <v>294</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -8457,10 +8523,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>283</v>
+        <v>295</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>284</v>
+        <v>296</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -8483,7 +8549,7 @@
         <v>74</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>285</v>
+        <v>297</v>
       </c>
       <c r="L70" s="2"/>
       <c r="M70" s="2"/>
@@ -8536,7 +8602,7 @@
         <v>74</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>286</v>
+        <v>298</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -8556,10 +8622,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>287</v>
+        <v>299</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>288</v>
+        <v>300</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -8582,7 +8648,7 @@
         <v>74</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>289</v>
+        <v>301</v>
       </c>
       <c r="L71" s="2"/>
       <c r="M71" s="2"/>
@@ -8635,7 +8701,7 @@
         <v>74</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>290</v>
+        <v>302</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -8655,10 +8721,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>291</v>
+        <v>303</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>292</v>
+        <v>304</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -8681,7 +8747,7 @@
         <v>74</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>293</v>
+        <v>305</v>
       </c>
       <c r="L72" s="2"/>
       <c r="M72" s="2"/>
@@ -8734,7 +8800,7 @@
         <v>74</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>294</v>
+        <v>306</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -8754,10 +8820,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>295</v>
+        <v>307</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>296</v>
+        <v>308</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -8780,7 +8846,7 @@
         <v>74</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>297</v>
+        <v>309</v>
       </c>
       <c r="L73" s="2"/>
       <c r="M73" s="2"/>
@@ -8833,7 +8899,7 @@
         <v>74</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>298</v>
+        <v>310</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -8853,10 +8919,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>299</v>
+        <v>311</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>300</v>
+        <v>312</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -8879,7 +8945,7 @@
         <v>74</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>301</v>
+        <v>313</v>
       </c>
       <c r="L74" s="2"/>
       <c r="M74" s="2"/>
@@ -8932,7 +8998,7 @@
         <v>74</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>302</v>
+        <v>314</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -8952,13 +9018,13 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>303</v>
+        <v>315</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="C75" t="s" s="2">
-        <v>304</v>
+        <v>316</v>
       </c>
       <c r="D75" t="s" s="2">
         <v>74</v>
@@ -8980,7 +9046,7 @@
         <v>74</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="L75" s="2"/>
       <c r="M75" s="2"/>
@@ -9033,7 +9099,7 @@
         <v>74</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -9053,10 +9119,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>240</v>
+        <v>252</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -9154,10 +9220,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>306</v>
+        <v>318</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -9255,10 +9321,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -9356,10 +9422,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>308</v>
+        <v>320</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -9457,10 +9523,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>248</v>
+        <v>260</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -9560,10 +9626,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>310</v>
+        <v>322</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -9663,10 +9729,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>311</v>
+        <v>323</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -9766,10 +9832,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>312</v>
+        <v>324</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>254</v>
+        <v>266</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -9869,10 +9935,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>313</v>
+        <v>325</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>256</v>
+        <v>268</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -9970,10 +10036,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>314</v>
+        <v>326</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>258</v>
+        <v>270</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -10003,7 +10069,7 @@
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="Q85" s="2"/>
       <c r="R85" t="s" s="2">
@@ -10029,7 +10095,7 @@
       </c>
       <c r="Y85" s="2"/>
       <c r="Z85" t="s" s="2">
-        <v>260</v>
+        <v>272</v>
       </c>
       <c r="AA85" t="s" s="2">
         <v>74</v>
@@ -10047,7 +10113,7 @@
         <v>74</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -10067,10 +10133,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>315</v>
+        <v>327</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -10104,7 +10170,7 @@
       </c>
       <c r="Q86" s="2"/>
       <c r="R86" t="s" s="2">
-        <v>264</v>
+        <v>276</v>
       </c>
       <c r="S86" t="s" s="2">
         <v>74</v>
@@ -10146,7 +10212,7 @@
         <v>74</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>265</v>
+        <v>277</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -10166,10 +10232,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>316</v>
+        <v>328</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>267</v>
+        <v>279</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -10192,7 +10258,7 @@
         <v>74</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>268</v>
+        <v>280</v>
       </c>
       <c r="L87" s="2"/>
       <c r="M87" s="2"/>
@@ -10245,7 +10311,7 @@
         <v>74</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -10265,10 +10331,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>317</v>
+        <v>329</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -10291,7 +10357,7 @@
         <v>74</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="L88" s="2"/>
       <c r="M88" s="2"/>
@@ -10344,7 +10410,7 @@
         <v>74</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -10364,10 +10430,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>318</v>
+        <v>330</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>275</v>
+        <v>287</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -10390,10 +10456,10 @@
         <v>74</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>319</v>
+        <v>331</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>320</v>
+        <v>332</v>
       </c>
       <c r="M89" s="2"/>
       <c r="N89" s="2"/>
@@ -10445,7 +10511,7 @@
         <v>74</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>278</v>
+        <v>290</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -10465,10 +10531,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>280</v>
+        <v>292</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -10491,7 +10557,7 @@
         <v>74</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>281</v>
+        <v>293</v>
       </c>
       <c r="L90" s="2"/>
       <c r="M90" s="2"/>
@@ -10544,7 +10610,7 @@
         <v>74</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>282</v>
+        <v>294</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -10564,10 +10630,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>322</v>
+        <v>334</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>284</v>
+        <v>296</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -10590,7 +10656,7 @@
         <v>74</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>285</v>
+        <v>297</v>
       </c>
       <c r="L91" s="2"/>
       <c r="M91" s="2"/>
@@ -10643,7 +10709,7 @@
         <v>74</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>286</v>
+        <v>298</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -10663,10 +10729,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>288</v>
+        <v>300</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -10689,7 +10755,7 @@
         <v>74</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>289</v>
+        <v>301</v>
       </c>
       <c r="L92" s="2"/>
       <c r="M92" s="2"/>
@@ -10742,7 +10808,7 @@
         <v>74</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>290</v>
+        <v>302</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -10762,10 +10828,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>324</v>
+        <v>336</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>292</v>
+        <v>304</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -10788,7 +10854,7 @@
         <v>74</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>293</v>
+        <v>305</v>
       </c>
       <c r="L93" s="2"/>
       <c r="M93" s="2"/>
@@ -10841,7 +10907,7 @@
         <v>74</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>294</v>
+        <v>306</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -10861,10 +10927,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>325</v>
+        <v>337</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>296</v>
+        <v>308</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -10887,7 +10953,7 @@
         <v>74</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>297</v>
+        <v>309</v>
       </c>
       <c r="L94" s="2"/>
       <c r="M94" s="2"/>
@@ -10940,7 +11006,7 @@
         <v>74</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>298</v>
+        <v>310</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -10960,10 +11026,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>326</v>
+        <v>338</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>300</v>
+        <v>312</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -10986,7 +11052,7 @@
         <v>74</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>301</v>
+        <v>313</v>
       </c>
       <c r="L95" s="2"/>
       <c r="M95" s="2"/>
@@ -11039,7 +11105,7 @@
         <v>74</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>302</v>
+        <v>314</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -11059,10 +11125,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>327</v>
+        <v>339</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>327</v>
+        <v>339</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -11085,12 +11151,16 @@
         <v>74</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="L96" s="2"/>
+        <v>340</v>
+      </c>
+      <c r="L96" t="s" s="2">
+        <v>341</v>
+      </c>
       <c r="M96" s="2"/>
       <c r="N96" s="2"/>
-      <c r="O96" s="2"/>
+      <c r="O96" t="s" s="2">
+        <v>342</v>
+      </c>
       <c r="P96" t="s" s="2">
         <v>74</v>
       </c>
@@ -11138,7 +11208,7 @@
         <v>74</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>327</v>
+        <v>339</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
@@ -11158,10 +11228,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>329</v>
+        <v>343</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>329</v>
+        <v>343</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -11259,10 +11329,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>330</v>
+        <v>344</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>330</v>
+        <v>344</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -11360,10 +11430,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>331</v>
+        <v>345</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>331</v>
+        <v>345</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -11461,10 +11531,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>332</v>
+        <v>346</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>332</v>
+        <v>346</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -11562,10 +11632,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>333</v>
+        <v>347</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>333</v>
+        <v>347</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -11665,10 +11735,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>334</v>
+        <v>348</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>334</v>
+        <v>348</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -11768,10 +11838,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>335</v>
+        <v>349</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>335</v>
+        <v>349</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -11871,10 +11941,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>336</v>
+        <v>350</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>336</v>
+        <v>350</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -11974,10 +12044,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>337</v>
+        <v>351</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>337</v>
+        <v>351</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -12075,10 +12145,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>338</v>
+        <v>352</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>338</v>
+        <v>352</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -12105,7 +12175,7 @@
       </c>
       <c r="L106" s="2"/>
       <c r="M106" t="s" s="2">
-        <v>339</v>
+        <v>353</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" s="2"/>
@@ -12114,7 +12184,7 @@
       </c>
       <c r="Q106" s="2"/>
       <c r="R106" t="s" s="2">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="S106" t="s" s="2">
         <v>74</v>
@@ -12156,7 +12226,7 @@
         <v>74</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>338</v>
+        <v>352</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -12176,10 +12246,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>340</v>
+        <v>354</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>340</v>
+        <v>354</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -12213,7 +12283,7 @@
       </c>
       <c r="Q107" s="2"/>
       <c r="R107" t="s" s="2">
-        <v>264</v>
+        <v>276</v>
       </c>
       <c r="S107" t="s" s="2">
         <v>74</v>
@@ -12255,7 +12325,7 @@
         <v>74</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>340</v>
+        <v>354</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
@@ -12275,10 +12345,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>341</v>
+        <v>355</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>341</v>
+        <v>355</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -12301,7 +12371,7 @@
         <v>74</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>342</v>
+        <v>356</v>
       </c>
       <c r="L108" s="2"/>
       <c r="M108" s="2"/>
@@ -12354,7 +12424,7 @@
         <v>74</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>341</v>
+        <v>355</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>75</v>
